--- a/data/Experiment/Raw/StomatalDensity.xlsx
+++ b/data/Experiment/Raw/StomatalDensity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B77E45-D2E4-E141-9704-E7718AE71D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCEF66F-94B8-7847-8F1F-B649619A331E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22520" windowHeight="17120" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="22520" windowHeight="17120" activeTab="3" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
   <sheets>
     <sheet name="PIPO" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="244">
   <si>
     <t>PIPO1</t>
   </si>
@@ -770,7 +770,7 @@
     <t>Stomata_n</t>
   </si>
   <si>
-    <t>StomatalDensity</t>
+    <t>StomatalDensity_n_mm-2</t>
   </si>
 </sst>
 </file>
@@ -2315,10 +2315,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B18CAA-D5E2-8F4D-8617-88F8364D5DB9}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2328,305 +2328,548 @@
       <c r="C1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" t="e">
+        <f>C2/B2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" t="e">
+        <f t="shared" ref="D3:D61" si="0">C3/B3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D14" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D16" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D18" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D19" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D22" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D23" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D24" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D26" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D29" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D30" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D31" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D32" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D33" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D34" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D35" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D36" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D37" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D38" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D39" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D40" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D41" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D42" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D44" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D45" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D46" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D47" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D48" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D49" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D50" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D51" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D52" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D53" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D54" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D55" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D56" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D57" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D58" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D59" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D60" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>120</v>
+      </c>
+      <c r="D61" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
@@ -2636,10 +2879,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E06963-B773-F348-8854-A3523910E721}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2649,305 +2892,548 @@
       <c r="C1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" t="e">
+        <f>C2/B2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" t="e">
+        <f t="shared" ref="D3:D61" si="0">C3/B3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D14" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D16" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D18" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D19" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D22" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D23" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D24" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D26" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D29" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D30" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D31" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D32" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D33" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D34" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D35" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D36" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D37" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D38" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D39" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D40" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D41" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D42" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D44" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D45" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D46" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D47" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D48" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D49" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D50" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D51" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D52" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D53" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D54" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D55" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D56" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D57" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D58" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D59" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D60" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>180</v>
+      </c>
+      <c r="D61" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
@@ -2957,10 +3443,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115E6809-C6E9-4B42-AF0B-D16D811C3B7F}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -2970,305 +3456,548 @@
       <c r="C1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" t="e">
+        <f>C2/B2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" t="e">
+        <f t="shared" ref="D3:D61" si="0">C3/B3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D14" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D16" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D18" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D19" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D21" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D22" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D23" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D24" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D25" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D26" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D27" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D29" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D30" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D31" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D32" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D33" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D34" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D35" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D36" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D37" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D38" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D39" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D40" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D41" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D42" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D44" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D45" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D46" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D47" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D48" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D49" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D50" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D51" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D52" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D53" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D54" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D55" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D56" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D57" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D58" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D59" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="D60" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>240</v>
+      </c>
+      <c r="D61" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>

--- a/data/Experiment/Raw/StomatalDensity.xlsx
+++ b/data/Experiment/Raw/StomatalDensity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCEF66F-94B8-7847-8F1F-B649619A331E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1E14B2-5B54-9145-91C7-1C711001F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22520" windowHeight="17120" activeTab="3" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="17820" windowHeight="17180" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
   <sheets>
     <sheet name="PIPO" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="244">
   <si>
     <t>PIPO1</t>
   </si>
@@ -1171,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F958DE17-0E59-E849-A835-10176DABDFD5}">
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1247,7 +1247,7 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D93" si="0">C5/B5</f>
+        <f t="shared" ref="D5:D109" si="0">C5/B5</f>
         <v>59.382422802850357</v>
       </c>
     </row>
@@ -1912,269 +1912,413 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D50" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="B50">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="C50">
+        <v>36</v>
+      </c>
+      <c r="D50">
+        <f t="shared" ref="D50" si="16">C50/B50</f>
+        <v>79.822616407982252</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="C51">
+        <v>47</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>77.42998352553542</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="C52">
+        <v>15</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>56.390977443609017</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D51" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
+      <c r="B53">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="C53">
+        <v>38</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="0"/>
+        <v>40.339702760084926</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54">
+        <v>1.091</v>
+      </c>
+      <c r="C54">
+        <v>52</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>47.662694775435384</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="C55">
+        <v>23</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>46.747967479674799</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D52" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
+      <c r="B56">
+        <v>0.622</v>
+      </c>
+      <c r="C56">
+        <v>26</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>41.80064308681672</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="C57">
+        <v>10</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ref="D57" si="17">C57/B57</f>
+        <v>21.459227467811157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="C58">
+        <v>23</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>39.861351819757367</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D53" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
+      <c r="B59">
+        <v>1.3839999999999999</v>
+      </c>
+      <c r="C59">
+        <v>82</v>
+      </c>
+      <c r="D59">
+        <f t="shared" ref="D59" si="18">C59/B59</f>
+        <v>59.248554913294804</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="C60">
+        <v>44</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ref="D60" si="19">C60/B60</f>
+        <v>68.217054263565885</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="C61">
+        <v>18</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>68.181818181818173</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D54" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
+      <c r="B62">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="C62">
+        <v>65</v>
+      </c>
+      <c r="D62">
+        <f t="shared" ref="D62:D63" si="20">C62/B62</f>
+        <v>59.633027522935777</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B63">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="C63">
+        <v>54</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="20"/>
+        <v>53.946053946053951</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="C64">
+        <v>29</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>54.307116104868911</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D55" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="s">
+      <c r="B65">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="C65">
+        <v>35</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>61.511423550087876</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B66">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="C66">
+        <v>47</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ref="D66" si="21">C66/B66</f>
+        <v>47.52275025278059</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="C67">
+        <v>47</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="0"/>
+        <v>44.804575786463303</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D56" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
+      <c r="B68">
+        <v>1.071</v>
+      </c>
+      <c r="C68">
+        <v>55</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="0"/>
+        <v>51.35387488328665</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="C69">
+        <v>35</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ref="D69" si="22">C69/B69</f>
+        <v>71.138211382113823</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="C70">
+        <v>34</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="0"/>
+        <v>39.48896631823461</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D57" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
+      <c r="B71">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="C71">
+        <v>30</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="0"/>
+        <v>44.91017964071856</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B72">
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="C72">
+        <v>49</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ref="D72" si="23">C72/B72</f>
+        <v>63.144329896907216</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="C73">
+        <v>31</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="0"/>
+        <v>59.730250481695563</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D58" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
+      <c r="D74" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D59" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
+      <c r="D75" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D60" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
+      <c r="D76" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D61" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
+      <c r="D77" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D62" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="3" t="s">
+      <c r="D78" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="D63" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D64" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D65" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D67" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D69" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D70" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D71" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D72" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D73" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D74" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D75" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D76" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D77" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D78" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D79" t="e">
         <f t="shared" si="0"/>
@@ -2183,7 +2327,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D80" t="e">
         <f t="shared" si="0"/>
@@ -2192,7 +2336,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D81" t="e">
         <f t="shared" si="0"/>
@@ -2201,7 +2345,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D82" t="e">
         <f t="shared" si="0"/>
@@ -2210,7 +2354,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D83" t="e">
         <f t="shared" si="0"/>
@@ -2219,7 +2363,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D84" t="e">
         <f t="shared" si="0"/>
@@ -2228,7 +2372,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D85" t="e">
         <f t="shared" si="0"/>
@@ -2237,7 +2381,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D86" t="e">
         <f t="shared" si="0"/>
@@ -2246,7 +2390,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D87" t="e">
         <f t="shared" si="0"/>
@@ -2255,7 +2399,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D88" t="e">
         <f t="shared" si="0"/>
@@ -2264,7 +2408,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D89" t="e">
         <f t="shared" si="0"/>
@@ -2273,7 +2417,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D90" t="e">
         <f t="shared" si="0"/>
@@ -2282,7 +2426,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D91" t="e">
         <f t="shared" si="0"/>
@@ -2291,7 +2435,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D92" t="e">
         <f t="shared" si="0"/>
@@ -2300,9 +2444,153 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D94" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D97" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D98" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D99" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D100" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D101" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D102" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D103" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D104" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D105" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D106" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D107" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D93" t="e">
+      <c r="D109" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>

--- a/data/Experiment/Raw/StomatalDensity.xlsx
+++ b/data/Experiment/Raw/StomatalDensity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1E14B2-5B54-9145-91C7-1C711001F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CA379B-61F5-8442-B05B-08B0C369C689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="17820" windowHeight="17180" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
+    <workbookView xWindow="16160" yWindow="5640" windowWidth="13240" windowHeight="12300" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
   <sheets>
     <sheet name="PIPO" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="244">
   <si>
     <t>PIPO1</t>
   </si>
@@ -831,12 +831,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1171,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F958DE17-0E59-E849-A835-10176DABDFD5}">
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1247,7 +1248,7 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D109" si="0">C5/B5</f>
+        <f t="shared" ref="D5:D143" si="0">C5/B5</f>
         <v>59.382422802850357</v>
       </c>
     </row>
@@ -2227,7 +2228,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B71">
@@ -2242,7 +2243,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B72">
@@ -2257,7 +2258,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B73">
@@ -2272,325 +2273,919 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D74" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="B74">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="C74">
+        <v>25</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="0"/>
+        <v>37.764350453172206</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75">
+        <v>0.26</v>
+      </c>
+      <c r="C75">
+        <v>16</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ref="D75" si="24">C75/B75</f>
+        <v>61.538461538461533</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="C76">
+        <v>43</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="0"/>
+        <v>43.967280163599185</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D75" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
+      <c r="B77">
+        <v>2.3010000000000002</v>
+      </c>
+      <c r="C77">
+        <v>126</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="0"/>
+        <v>54.758800521512384</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78">
+        <v>1.734</v>
+      </c>
+      <c r="C78">
+        <v>122</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ref="D78" si="25">C78/B78</f>
+        <v>70.357554786620526</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79">
+        <v>0.378</v>
+      </c>
+      <c r="C79">
+        <v>18</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="0"/>
+        <v>47.61904761904762</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D76" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
+      <c r="B80">
+        <v>0.85</v>
+      </c>
+      <c r="C80">
+        <v>63</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="0"/>
+        <v>74.117647058823536</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B81">
+        <v>1.069</v>
+      </c>
+      <c r="C81">
+        <v>64</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ref="D81" si="26">C81/B81</f>
+        <v>59.869036482694106</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B82">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="C82">
+        <v>17</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="0"/>
+        <v>51.051051051051047</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D77" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
+      <c r="B83">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="C83">
+        <v>36</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="0"/>
+        <v>54.13533834586466</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B84">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="C84">
+        <v>41</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ref="D84" si="27">C84/B84</f>
+        <v>60.117302052785917</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85">
+        <v>0.67</v>
+      </c>
+      <c r="C85">
+        <v>43</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="0"/>
+        <v>64.179104477611943</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D78" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
+      <c r="B86">
+        <v>1.248</v>
+      </c>
+      <c r="C86">
+        <v>57</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="0"/>
+        <v>45.67307692307692</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B87">
+        <v>1.4159999999999999</v>
+      </c>
+      <c r="C87">
+        <v>58</v>
+      </c>
+      <c r="D87">
+        <f t="shared" ref="D87" si="28">C87/B87</f>
+        <v>40.960451977401135</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88">
+        <v>0.311</v>
+      </c>
+      <c r="C88">
+        <v>23</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="0"/>
+        <v>73.954983922829584</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D79" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
+      <c r="B89">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="C89">
+        <v>22</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="0"/>
+        <v>39.426523297491038</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B90">
+        <v>1.0409999999999999</v>
+      </c>
+      <c r="C90">
+        <v>64</v>
+      </c>
+      <c r="D90">
+        <f t="shared" ref="D90" si="29">C90/B90</f>
+        <v>61.47934678194045</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B91">
+        <v>0.628</v>
+      </c>
+      <c r="C91">
+        <v>33</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="0"/>
+        <v>52.547770700636946</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D80" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
+      <c r="B92">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="C92">
+        <v>39</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="0"/>
+        <v>49.304677623261689</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93">
+        <v>1.5669999999999999</v>
+      </c>
+      <c r="C93">
+        <v>83</v>
+      </c>
+      <c r="D93">
+        <f t="shared" ref="D93" si="30">C93/B93</f>
+        <v>52.967453733248249</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="C94">
+        <v>46</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="0"/>
+        <v>50.438596491228068</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D81" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
+      <c r="B95">
+        <v>0.81</v>
+      </c>
+      <c r="C95">
+        <v>48</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="0"/>
+        <v>59.259259259259252</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="C96">
+        <v>31</v>
+      </c>
+      <c r="D96">
+        <f t="shared" ref="D96" si="31">C96/B96</f>
+        <v>38.509316770186331</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="C97">
+        <v>48</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="0"/>
+        <v>70.072992700729927</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D82" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
+      <c r="B98">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="C98">
+        <v>29</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="0"/>
+        <v>40.960451977401135</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99">
+        <v>0.622</v>
+      </c>
+      <c r="C99">
+        <v>41</v>
+      </c>
+      <c r="D99">
+        <f t="shared" ref="D99" si="32">C99/B99</f>
+        <v>65.916398713826368</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="C100">
+        <v>30</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="0"/>
+        <v>39.113428943937414</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D83" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
+      <c r="B101">
+        <v>0.372</v>
+      </c>
+      <c r="C101">
+        <v>27</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="0"/>
+        <v>72.58064516129032</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="C102">
+        <v>40</v>
+      </c>
+      <c r="D102">
+        <f t="shared" ref="D102" si="33">C102/B102</f>
+        <v>78.895463510848131</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B103">
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="C103">
+        <v>86</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="0"/>
+        <v>51.932367149758456</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D84" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="2" t="s">
+      <c r="B104">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="C104">
+        <v>56</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="0"/>
+        <v>46.473029045643152</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B105">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="C105">
+        <v>76</v>
+      </c>
+      <c r="D105">
+        <f t="shared" ref="D105" si="34">C105/B105</f>
+        <v>63.070539419087133</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="C106">
+        <v>50</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="0"/>
+        <v>52.301255230125527</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D85" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="2" t="s">
+      <c r="B107">
+        <v>1.595</v>
+      </c>
+      <c r="C107">
+        <v>93</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="0"/>
+        <v>58.307210031347964</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B108">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="C108">
+        <v>23</v>
+      </c>
+      <c r="D108">
+        <f t="shared" ref="D108" si="35">C108/B108</f>
+        <v>69.908814589665653</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B109">
+        <v>1.2490000000000001</v>
+      </c>
+      <c r="C109">
+        <v>65</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="0"/>
+        <v>52.041633306645309</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D86" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="2" t="s">
+      <c r="B110">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="C110">
+        <v>21</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="0"/>
+        <v>75.53956834532373</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B111">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="C111">
+        <v>64</v>
+      </c>
+      <c r="D111">
+        <f t="shared" ref="D111" si="36">C111/B111</f>
+        <v>90.395480225988706</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B112">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="C112">
+        <v>47</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="0"/>
+        <v>84.380610412926387</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D87" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="2" t="s">
+      <c r="B113">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="C113">
+        <v>17</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="0"/>
+        <v>43.814432989690722</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="C114">
+        <v>25</v>
+      </c>
+      <c r="D114">
+        <f t="shared" ref="D114" si="37">C114/B114</f>
+        <v>51.546391752577321</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B115">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="C115">
+        <v>42</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="0"/>
+        <v>47.032474804031352</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D88" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="2" t="s">
+      <c r="B116">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="C116">
+        <v>56</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="0"/>
+        <v>40.172166427546628</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B117">
+        <v>0.625</v>
+      </c>
+      <c r="C117">
+        <v>34</v>
+      </c>
+      <c r="D117">
+        <f t="shared" ref="D117" si="38">C117/B117</f>
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B118">
+        <v>0.39</v>
+      </c>
+      <c r="C118">
+        <v>17</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="0"/>
+        <v>43.589743589743591</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D89" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="2" t="s">
+      <c r="B119">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="C119">
+        <v>27</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="0"/>
+        <v>54.878048780487809</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120">
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="C120">
+        <v>37</v>
+      </c>
+      <c r="D120">
+        <f t="shared" ref="D120" si="39">C120/B120</f>
+        <v>55.722891566265055</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="C121">
+        <v>44</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="0"/>
+        <v>55.55555555555555</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D90" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="2" t="s">
+      <c r="D122" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" t="e">
+        <f t="shared" ref="D123" si="40">C123/B123</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D91" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
+      <c r="D125" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D92" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
+      <c r="D126" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D93" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
+      <c r="D127" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D94" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
+      <c r="D128" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D95" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
+      <c r="D129" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D96" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
+      <c r="D130" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D97" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="2" t="s">
+      <c r="D131" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D98" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
+      <c r="D132" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D99" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="2" t="s">
+      <c r="D133" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D100" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
+      <c r="D134" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D101" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="2" t="s">
+      <c r="D135" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D102" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
+      <c r="D136" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D103" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="2" t="s">
+      <c r="D137" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D104" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
+      <c r="D138" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D105" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
+      <c r="D139" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D106" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="2" t="s">
+      <c r="D140" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D107" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="2" t="s">
+      <c r="D141" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D108" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="2" t="s">
+      <c r="D142" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D109" t="e">
+      <c r="D143" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>

--- a/data/Experiment/Raw/StomatalDensity.xlsx
+++ b/data/Experiment/Raw/StomatalDensity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CA379B-61F5-8442-B05B-08B0C369C689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967ED056-FC8F-9443-B141-EC87796E49A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16160" yWindow="5640" windowWidth="13240" windowHeight="12300" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
+    <workbookView xWindow="15640" yWindow="5900" windowWidth="13120" windowHeight="12060" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
   <sheets>
     <sheet name="PIPO" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="244">
   <si>
     <t>PIPO1</t>
   </si>
@@ -1172,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F958DE17-0E59-E849-A835-10176DABDFD5}">
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1248,7 +1248,7 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D143" si="0">C5/B5</f>
+        <f t="shared" ref="D5:D147" si="0">C5/B5</f>
         <v>59.382422802850357</v>
       </c>
     </row>
@@ -2993,89 +2993,143 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D122" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="B122">
+        <v>1.4410000000000001</v>
+      </c>
+      <c r="C122">
+        <v>94</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="0"/>
+        <v>65.232477446217899</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D123" t="e">
+      <c r="B123">
+        <v>1.4690000000000001</v>
+      </c>
+      <c r="C123">
+        <v>106</v>
+      </c>
+      <c r="D123">
         <f t="shared" ref="D123" si="40">C123/B123</f>
-        <v>#DIV/0!</v>
+        <v>72.157930565010204</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D124" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="B124">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="C124">
+        <v>75</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="0"/>
+        <v>75.452716297786722</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D125" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="B125">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="C125">
+        <v>34</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="0"/>
+        <v>74.074074074074076</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D126" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="A126" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B126">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="C126">
+        <v>45</v>
+      </c>
+      <c r="D126">
+        <f t="shared" ref="D126" si="41">C126/B126</f>
+        <v>60.646900269541781</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D127" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="A127" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B127">
+        <v>1.109</v>
+      </c>
+      <c r="C127">
+        <v>56</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="0"/>
+        <v>50.495942290351671</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D128" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>43</v>
+      </c>
+      <c r="B128">
+        <v>1.56</v>
+      </c>
+      <c r="C128">
+        <v>81</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="0"/>
+        <v>51.92307692307692</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D129" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>43</v>
+      </c>
+      <c r="B129">
+        <v>1.0740000000000001</v>
+      </c>
+      <c r="C129">
+        <v>51</v>
+      </c>
+      <c r="D129">
+        <f t="shared" ref="D129" si="42">C129/B129</f>
+        <v>47.486033519553068</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D130" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>43</v>
+      </c>
+      <c r="B130">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="C130">
+        <v>22</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="0"/>
+        <v>61.624649859943979</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D131" t="e">
         <f t="shared" si="0"/>
@@ -3084,7 +3138,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D132" t="e">
         <f t="shared" si="0"/>
@@ -3093,7 +3147,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D133" t="e">
         <f t="shared" si="0"/>
@@ -3102,7 +3156,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D134" t="e">
         <f t="shared" si="0"/>
@@ -3111,7 +3165,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D135" t="e">
         <f t="shared" si="0"/>
@@ -3120,7 +3174,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D136" t="e">
         <f t="shared" si="0"/>
@@ -3129,7 +3183,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D137" t="e">
         <f t="shared" si="0"/>
@@ -3138,7 +3192,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D138" t="e">
         <f t="shared" si="0"/>
@@ -3147,7 +3201,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D139" t="e">
         <f t="shared" si="0"/>
@@ -3156,7 +3210,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D140" t="e">
         <f t="shared" si="0"/>
@@ -3165,7 +3219,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D141" t="e">
         <f t="shared" si="0"/>
@@ -3174,7 +3228,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D142" t="e">
         <f t="shared" si="0"/>
@@ -3183,9 +3237,45 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D143" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D144" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D145" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D146" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D143" t="e">
+      <c r="D147" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>

--- a/data/Experiment/Raw/StomatalDensity.xlsx
+++ b/data/Experiment/Raw/StomatalDensity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967ED056-FC8F-9443-B141-EC87796E49A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF2985D-383D-0640-A889-57FED081192B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15640" yWindow="5900" windowWidth="13120" windowHeight="12060" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="244">
   <si>
     <t>PIPO1</t>
   </si>
@@ -1172,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F958DE17-0E59-E849-A835-10176DABDFD5}">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1248,7 +1248,7 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D147" si="0">C5/B5</f>
+        <f t="shared" ref="D5:D153" si="0">C5/B5</f>
         <v>59.382422802850357</v>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B128">
@@ -3098,7 +3098,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B129">
@@ -3113,7 +3113,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B130">
@@ -3128,89 +3128,143 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D131" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="B131">
+        <v>1.083</v>
+      </c>
+      <c r="C131">
+        <v>70</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="0"/>
+        <v>64.635272391505083</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B132">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="C132">
+        <v>30</v>
+      </c>
+      <c r="D132">
+        <f t="shared" ref="D132" si="43">C132/B132</f>
+        <v>65.934065934065927</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B133">
+        <v>0.249</v>
+      </c>
+      <c r="C133">
+        <v>11</v>
+      </c>
+      <c r="D133">
+        <f t="shared" si="0"/>
+        <v>44.176706827309239</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D132" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133" s="2" t="s">
+      <c r="B134">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="C134">
+        <v>38</v>
+      </c>
+      <c r="D134">
+        <f t="shared" si="0"/>
+        <v>49.414824447334198</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B135">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="C135">
+        <v>40</v>
+      </c>
+      <c r="D135">
+        <f t="shared" ref="D135" si="44">C135/B135</f>
+        <v>52.015604681404419</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B136">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="C136">
+        <v>10</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="0"/>
+        <v>48.07692307692308</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D133" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D134" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D135" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D136" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D137" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="B137">
+        <v>1.659</v>
+      </c>
+      <c r="C137">
+        <v>88</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="0"/>
+        <v>53.044002411091014</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D138" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="A138" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B138">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C138">
+        <v>44</v>
+      </c>
+      <c r="D138">
+        <f t="shared" ref="D138" si="45">C138/B138</f>
+        <v>75.862068965517253</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D139" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="A139" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B139">
+        <v>1.3680000000000001</v>
+      </c>
+      <c r="C139">
+        <v>73</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="0"/>
+        <v>53.362573099415201</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D140" t="e">
         <f t="shared" si="0"/>
@@ -3219,7 +3273,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D141" t="e">
         <f t="shared" si="0"/>
@@ -3228,7 +3282,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D142" t="e">
         <f t="shared" si="0"/>
@@ -3237,7 +3291,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D143" t="e">
         <f t="shared" si="0"/>
@@ -3246,7 +3300,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D144" t="e">
         <f t="shared" si="0"/>
@@ -3255,7 +3309,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D145" t="e">
         <f t="shared" si="0"/>
@@ -3264,7 +3318,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D146" t="e">
         <f t="shared" si="0"/>
@@ -3273,9 +3327,63 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D147" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D148" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D149" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D150" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D151" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D152" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D147" t="e">
+      <c r="D153" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
